--- a/data/horaires_paleo.xlsx
+++ b/data/horaires_paleo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF74BD0-D80F-42DF-9C72-296FD3917C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2ABDC6-85E0-4F4F-9DAD-6DE9FE065001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="1480" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="139">
   <si>
     <t>GS</t>
   </si>
@@ -431,6 +431,33 @@
   </si>
   <si>
     <t>Grande Scène</t>
+  </si>
+  <si>
+    <t>La Ruche</t>
+  </si>
+  <si>
+    <t>Phusis</t>
+  </si>
+  <si>
+    <t>T'es rien sans la terre</t>
+  </si>
+  <si>
+    <t>Spoutnik Disko Mobil</t>
+  </si>
+  <si>
+    <t>Volkanik</t>
+  </si>
+  <si>
+    <t>Surprises foraines</t>
+  </si>
+  <si>
+    <t>Les PCGB</t>
+  </si>
+  <si>
+    <t>Les Frères Jacquard</t>
+  </si>
+  <si>
+    <t>Durée</t>
   </si>
 </sst>
 </file>
@@ -438,7 +465,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="[$-100C]dddd\ d"/>
+    <numFmt numFmtId="164" formatCode="[$-100C]dddd\ d"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -797,24 +824,41 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -828,23 +872,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1153,31 +1180,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E65E8F0-2291-41D9-9A9A-CE313C5B899E}">
-  <dimension ref="A1:C148"/>
+  <dimension ref="A1:D199"/>
   <sheetFormatPr defaultRowHeight="12.45" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.15234375" style="34" customWidth="1"/>
-    <col min="2" max="3" width="15.4609375" style="33" customWidth="1"/>
+    <col min="1" max="1" width="34.15234375" style="26" customWidth="1"/>
+    <col min="2" max="3" width="15.4609375" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="22.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="25"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="35">
+      <c r="A3" s="27">
         <v>46224</v>
       </c>
       <c r="B3" s="17"/>
@@ -1217,7 +1244,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="35">
+      <c r="A7" s="27">
         <v>46225</v>
       </c>
       <c r="B7" s="17"/>
@@ -1257,7 +1284,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="35">
+      <c r="A11" s="27">
         <v>46226</v>
       </c>
       <c r="B11" s="17" t="s">
@@ -1299,7 +1326,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="35">
+      <c r="A15" s="27">
         <v>46227</v>
       </c>
       <c r="B15" s="17" t="s">
@@ -1341,7 +1368,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="35">
+      <c r="A19" s="27">
         <v>46228</v>
       </c>
       <c r="B19" s="17" t="s">
@@ -1383,7 +1410,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="35">
+      <c r="A23" s="27">
         <v>46229</v>
       </c>
       <c r="B23" s="17" t="s">
@@ -1425,28 +1452,28 @@
       </c>
     </row>
     <row r="27" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="38"/>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
     </row>
     <row r="28" spans="1:3" ht="22.75" x14ac:dyDescent="0.3">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="25"/>
+      <c r="C29" s="32"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="35">
+      <c r="A30" s="27">
         <v>46224</v>
       </c>
       <c r="B30" s="17"/>
@@ -1486,7 +1513,7 @@
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="35">
+      <c r="A34" s="27">
         <v>46225</v>
       </c>
       <c r="B34" s="17" t="s">
@@ -1528,7 +1555,7 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="35">
+      <c r="A38" s="27">
         <v>46226</v>
       </c>
       <c r="B38" s="17" t="s">
@@ -1581,7 +1608,7 @@
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="35">
+      <c r="A43" s="27">
         <v>46227</v>
       </c>
       <c r="B43" s="17" t="s">
@@ -1634,7 +1661,7 @@
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="35">
+      <c r="A48" s="27">
         <v>46228</v>
       </c>
       <c r="B48" s="17" t="s">
@@ -1687,7 +1714,7 @@
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="35">
+      <c r="A53" s="27">
         <v>46229</v>
       </c>
       <c r="B53" s="17" t="s">
@@ -1729,28 +1756,28 @@
       </c>
     </row>
     <row r="57" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="38"/>
-      <c r="B57" s="39"/>
-      <c r="C57" s="39"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
     </row>
     <row r="58" spans="1:3" ht="22.75" x14ac:dyDescent="0.3">
-      <c r="A58" s="36" t="s">
+      <c r="A58" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B59" s="25" t="s">
+      <c r="B59" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C59" s="25"/>
+      <c r="C59" s="32"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="35">
+      <c r="A60" s="27">
         <v>46224</v>
       </c>
       <c r="B60" s="17"/>
@@ -1801,7 +1828,7 @@
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="35">
+      <c r="A65" s="27">
         <v>46225</v>
       </c>
       <c r="B65" s="17" t="s">
@@ -1854,7 +1881,7 @@
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="35">
+      <c r="A70" s="27">
         <v>46226</v>
       </c>
       <c r="B70" s="17" t="s">
@@ -1907,7 +1934,7 @@
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="35">
+      <c r="A75" s="27">
         <v>46227</v>
       </c>
       <c r="B75" s="17" t="s">
@@ -1960,7 +1987,7 @@
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="35">
+      <c r="A80" s="27">
         <v>46228</v>
       </c>
       <c r="B80" s="17" t="s">
@@ -2013,7 +2040,7 @@
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="35">
+      <c r="A85" s="27">
         <v>46229</v>
       </c>
       <c r="B85" s="17" t="s">
@@ -2066,28 +2093,28 @@
       </c>
     </row>
     <row r="90" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="38"/>
-      <c r="B90" s="39"/>
-      <c r="C90" s="39"/>
+      <c r="A90" s="28"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
     </row>
     <row r="91" spans="1:3" ht="22.75" x14ac:dyDescent="0.3">
-      <c r="A91" s="36" t="s">
+      <c r="A91" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B91" s="37"/>
-      <c r="C91" s="37"/>
+      <c r="B91" s="31"/>
+      <c r="C91" s="31"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B92" s="25" t="s">
+      <c r="B92" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C92" s="25"/>
+      <c r="C92" s="32"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="35">
+      <c r="A93" s="27">
         <v>46224</v>
       </c>
       <c r="B93" s="17"/>
@@ -2127,7 +2154,7 @@
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="35">
+      <c r="A97" s="27">
         <v>46225</v>
       </c>
       <c r="B97" s="17" t="s">
@@ -2169,7 +2196,7 @@
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="35">
+      <c r="A101" s="27">
         <v>46226</v>
       </c>
       <c r="B101" s="17" t="s">
@@ -2211,7 +2238,7 @@
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="35">
+      <c r="A105" s="27">
         <v>46227</v>
       </c>
       <c r="B105" s="17" t="s">
@@ -2253,7 +2280,7 @@
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="35">
+      <c r="A109" s="27">
         <v>46228</v>
       </c>
       <c r="B109" s="17" t="s">
@@ -2295,7 +2322,7 @@
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="35">
+      <c r="A113" s="27">
         <v>46229</v>
       </c>
       <c r="B113" s="17" t="s">
@@ -2337,28 +2364,28 @@
       </c>
     </row>
     <row r="117" spans="1:3" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="38"/>
-      <c r="B117" s="39"/>
-      <c r="C117" s="39"/>
+      <c r="A117" s="28"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118" spans="1:3" ht="22.75" x14ac:dyDescent="0.3">
-      <c r="A118" s="36" t="s">
+      <c r="A118" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B118" s="37"/>
-      <c r="C118" s="37"/>
+      <c r="B118" s="31"/>
+      <c r="C118" s="31"/>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B119" s="25" t="s">
+      <c r="B119" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C119" s="25"/>
+      <c r="C119" s="32"/>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="35">
+      <c r="A120" s="27">
         <v>46224</v>
       </c>
       <c r="B120" s="17"/>
@@ -2409,7 +2436,7 @@
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="35">
+      <c r="A125" s="27">
         <v>46225</v>
       </c>
       <c r="B125" s="17" t="s">
@@ -2462,7 +2489,7 @@
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="35">
+      <c r="A130" s="27">
         <v>46226</v>
       </c>
       <c r="B130" s="17" t="s">
@@ -2515,7 +2542,7 @@
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="35">
+      <c r="A135" s="27">
         <v>46227</v>
       </c>
       <c r="B135" s="17" t="s">
@@ -2568,7 +2595,7 @@
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="35">
+      <c r="A140" s="27">
         <v>46228</v>
       </c>
       <c r="B140" s="17" t="s">
@@ -2620,8 +2647,8 @@
         <v>1.0451388888888888</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="35">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="27">
         <v>46229</v>
       </c>
       <c r="B145" s="17" t="s">
@@ -2629,7 +2656,7 @@
       </c>
       <c r="C145" s="18"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="20" t="s">
         <v>126</v>
       </c>
@@ -2640,7 +2667,7 @@
         <v>0.79166666666666663</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="20" t="s">
         <v>127</v>
       </c>
@@ -2651,7 +2678,7 @@
         <v>0.90277777777777779</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="20" t="s">
         <v>128</v>
       </c>
@@ -2662,8 +2689,731 @@
         <v>1.0381944444444444</v>
       </c>
     </row>
+    <row r="149" spans="1:4" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="28"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
+    </row>
+    <row r="150" spans="1:4" ht="22.75" x14ac:dyDescent="0.3">
+      <c r="A150" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B150" s="31"/>
+      <c r="C150" s="31"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B151" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C151" s="32"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="27">
+        <v>46224</v>
+      </c>
+      <c r="B152" s="17"/>
+      <c r="C152" s="18"/>
+      <c r="D152" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B153" s="21">
+        <v>0.71875</v>
+      </c>
+      <c r="C153" s="22">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D153" s="25">
+        <f>C153-B153</f>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B154" s="21">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="C154" s="22">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="D154" s="25">
+        <f t="shared" ref="D154:D199" si="0">C154-B154</f>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B155" s="21">
+        <v>0.8125</v>
+      </c>
+      <c r="C155" s="22">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D155" s="25">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B156" s="21">
+        <v>0.86458333333333337</v>
+      </c>
+      <c r="C156" s="22">
+        <v>0.92013888888888884</v>
+      </c>
+      <c r="D156" s="25">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555469E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B157" s="21">
+        <v>0.92708333333333337</v>
+      </c>
+      <c r="C157" s="22">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="D157" s="25">
+        <f t="shared" si="0"/>
+        <v>2.0833333333333259E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B158" s="21">
+        <v>0.95486111111111116</v>
+      </c>
+      <c r="C158" s="22">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="D158" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B159" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C159" s="22">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D159" s="25">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="27">
+        <v>46225</v>
+      </c>
+      <c r="B160" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C160" s="18"/>
+      <c r="D160" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B161" s="21">
+        <v>0.6875</v>
+      </c>
+      <c r="C161" s="22">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D161" s="25">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B162" s="21">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="C162" s="22">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D162" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B163" s="21">
+        <v>0.80208333333333337</v>
+      </c>
+      <c r="C163" s="22">
+        <v>0.84375</v>
+      </c>
+      <c r="D163" s="25">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B164" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C164" s="22">
+        <v>0.875</v>
+      </c>
+      <c r="D164" s="25">
+        <f t="shared" si="0"/>
+        <v>2.083333333333337E-2</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B165" s="21">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="C165" s="22">
+        <v>0.95138888888888884</v>
+      </c>
+      <c r="D165" s="25">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555469E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B166" s="21">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C166" s="22">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="D166" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B167" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C167" s="22">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D167" s="25">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="27">
+        <v>46226</v>
+      </c>
+      <c r="B168" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C168" s="18"/>
+      <c r="D168" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B169" s="21">
+        <v>0.6875</v>
+      </c>
+      <c r="C169" s="22">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="D169" s="25">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B170" s="21">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="C170" s="22">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D170" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B171" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C171" s="22">
+        <v>0.8125</v>
+      </c>
+      <c r="D171" s="25">
+        <f t="shared" si="0"/>
+        <v>2.083333333333337E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B172" s="21">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C172" s="22">
+        <v>0.875</v>
+      </c>
+      <c r="D172" s="25">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B173" s="21">
+        <v>0.89236111111111116</v>
+      </c>
+      <c r="C173" s="22">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="D173" s="25">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555469E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B174" s="21">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C174" s="22">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="D174" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B175" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C175" s="22">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D175" s="25">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="27">
+        <v>46227</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C176" s="18"/>
+      <c r="D176" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B177" s="21">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C177" s="22">
+        <v>0.71875</v>
+      </c>
+      <c r="D177" s="25">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B178" s="21">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C178" s="22">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D178" s="25">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666741E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B179" s="21">
+        <v>0.8125</v>
+      </c>
+      <c r="C179" s="22">
+        <v>0.84375</v>
+      </c>
+      <c r="D179" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B180" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="C180" s="22">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="D180" s="25">
+        <f t="shared" si="0"/>
+        <v>5.555555555555558E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B181" s="21">
+        <v>0.93055555555555558</v>
+      </c>
+      <c r="C181" s="22">
+        <v>0.95138888888888884</v>
+      </c>
+      <c r="D181" s="25">
+        <f t="shared" si="0"/>
+        <v>2.0833333333333259E-2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B182" s="21">
+        <v>0.96180555555555558</v>
+      </c>
+      <c r="C182" s="22">
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="D182" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B183" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C183" s="22">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D183" s="25">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="27">
+        <v>46228</v>
+      </c>
+      <c r="B184" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C184" s="18"/>
+      <c r="D184" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B185" s="21">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="C185" s="22">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D185" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B186" s="21">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C186" s="22">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="D186" s="25">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666741E-2</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B187" s="21">
+        <v>0.78819444444444442</v>
+      </c>
+      <c r="C187" s="22">
+        <v>0.82986111111111116</v>
+      </c>
+      <c r="D187" s="25">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666741E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B188" s="21">
+        <v>0.84027777777777779</v>
+      </c>
+      <c r="C188" s="22">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D188" s="25">
+        <f t="shared" si="0"/>
+        <v>5.555555555555558E-2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B189" s="21">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C189" s="22">
+        <v>0.9375</v>
+      </c>
+      <c r="D189" s="25">
+        <f t="shared" si="0"/>
+        <v>2.083333333333337E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B190" s="21">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="C190" s="22">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="D190" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B191" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C191" s="22">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D191" s="25">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" s="27">
+        <v>46229</v>
+      </c>
+      <c r="B192" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C192" s="18"/>
+      <c r="D192" s="25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="B193" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C193" s="22">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D193" s="25">
+        <f t="shared" si="0"/>
+        <v>4.1666666666666741E-2</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B194" s="21">
+        <v>0.71875</v>
+      </c>
+      <c r="C194" s="22">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="D194" s="25">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B195" s="21">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="C195" s="22">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="D195" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="B196" s="21">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="C196" s="22">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D196" s="25">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555469E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B197" s="21">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="C197" s="22">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="D197" s="25">
+        <f t="shared" si="0"/>
+        <v>2.083333333333337E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198" s="21">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C198" s="22">
+        <v>0.94791666666666663</v>
+      </c>
+      <c r="D198" s="25">
+        <f t="shared" si="0"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B199" s="21">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C199" s="22">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D199" s="25">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="B151:C151"/>
     <mergeCell ref="A91:C91"/>
     <mergeCell ref="B92:C92"/>
     <mergeCell ref="A118:C118"/>
@@ -2704,52 +3454,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30.45" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="B1" s="29" t="e">
+      <c r="B1" s="33" t="e">
         <f>_xlfn.XLOOKUP(B2,#REF!,#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:16" s="2" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="32"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:16" s="4" customFormat="1" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="e">
+      <c r="A3" s="34" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
       <c r="M3" s="3" t="e">
         <f>A3</f>
         <v>#REF!</v>
@@ -2760,21 +3510,21 @@
       <c r="C4" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28" t="s">
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="26" t="s">
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
       <c r="M4" s="6" t="e">
         <f t="shared" ref="M4:M10" si="0">M3</f>
         <v>#REF!</v>
@@ -3129,21 +3879,21 @@
       </c>
     </row>
     <row r="11" spans="1:16" s="4" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="e">
+      <c r="A11" s="34" t="e">
         <f>A3+1</f>
         <v>#REF!</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="3" t="e">
         <f>A11</f>
         <v>#REF!</v>
@@ -3154,21 +3904,21 @@
       <c r="C12" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28"/>
-      <c r="G12" s="28" t="s">
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="26" t="s">
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
       <c r="M12" s="6" t="e">
         <f t="shared" ref="M12:M18" si="4">M11</f>
         <v>#REF!</v>
@@ -3493,21 +4243,21 @@
       </c>
     </row>
     <row r="19" spans="1:13" s="4" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="27" t="e">
+      <c r="A19" s="34" t="e">
         <f>A11+1</f>
         <v>#REF!</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
       <c r="M19" s="3" t="e">
         <f>A19</f>
         <v>#REF!</v>
@@ -3518,21 +4268,21 @@
       <c r="C20" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="26" t="s">
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="26"/>
-      <c r="L20" s="26"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
       <c r="M20" s="6" t="e">
         <f t="shared" ref="M20:M26" si="8">M19</f>
         <v>#REF!</v>
@@ -3857,21 +4607,21 @@
       </c>
     </row>
     <row r="27" spans="1:13" s="4" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A27" s="27" t="e">
+      <c r="A27" s="34" t="e">
         <f>A19+1</f>
         <v>#REF!</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
       <c r="M27" s="3" t="e">
         <f>A27</f>
         <v>#REF!</v>
@@ -3882,21 +4632,21 @@
       <c r="C28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28" t="s">
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="26" t="s">
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K28" s="26"/>
-      <c r="L28" s="26"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
       <c r="M28" s="6" t="e">
         <f t="shared" ref="M28:M34" si="12">M27</f>
         <v>#REF!</v>
@@ -4221,21 +4971,21 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="4" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="27" t="e">
+      <c r="A35" s="34" t="e">
         <f>A27+1</f>
         <v>#REF!</v>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="3" t="e">
         <f>A35</f>
         <v>#REF!</v>
@@ -4246,21 +4996,21 @@
       <c r="C36" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28" t="s">
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="26" t="s">
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
       <c r="M36" s="6" t="e">
         <f t="shared" ref="M36:M42" si="16">M35</f>
         <v>#REF!</v>
@@ -4585,21 +5335,21 @@
       </c>
     </row>
     <row r="43" spans="1:13" s="4" customFormat="1" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A43" s="27" t="e">
+      <c r="A43" s="34" t="e">
         <f>A35+1</f>
         <v>#REF!</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
       <c r="M43" s="3" t="e">
         <f>A43</f>
         <v>#REF!</v>
@@ -4610,21 +5360,21 @@
       <c r="C44" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="28" t="s">
+      <c r="D44" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28" t="s">
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="26" t="s">
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
       <c r="M44" s="6" t="e">
         <f t="shared" ref="M44:M52" si="20">M43</f>
         <v>#REF!</v>
@@ -4977,6 +5727,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="A19:L19"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G44:I44"/>
     <mergeCell ref="B1:L1"/>
     <mergeCell ref="A35:L35"/>
     <mergeCell ref="J4:L4"/>
@@ -4993,75 +5753,29 @@
     <mergeCell ref="D20:F20"/>
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="A43:L43"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="G44:I44"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:L2" xr:uid="{5C23BFC7-05B5-4456-83A4-6A8FBF73A3F0}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15748031496062992" right="0.15748031496062992" top="0.28000000000000003" bottom="0.39" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Arial,Gras italique"&amp;8PALEO FESTIVAL NYON&amp;R&amp;"Arial,Gras italique"&amp;8Situation au &amp;D, &amp;T</oddFooter>
   </headerFooter>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5C23BFC7-05B5-4456-83A4-6A8FBF73A3F0}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:L2</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c7fc7845-db9b-43ce-aae6-d5b1cef6895c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="849af248-afc5-4274-81e2-3a489a8759ff">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <SharedWithUsers xmlns="c7fc7845-db9b-43ce-aae6-d5b1cef6895c">
-      <UserInfo>
-        <DisplayName>Christophe PLATEL</DisplayName>
-        <AccountId>72</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Média Paléo</DisplayName>
-        <AccountId>793</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Presse@paleo.ch</DisplayName>
-        <AccountId>800</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Malika DJEHICHE</DisplayName>
-        <AccountId>276</AccountId>
-        <AccountType/>
-      </UserInfo>
-      <UserInfo>
-        <DisplayName>Michèle MÜLLER</DisplayName>
-        <AccountId>56</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5320,27 +6034,47 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c7fc7845-db9b-43ce-aae6-d5b1cef6895c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="849af248-afc5-4274-81e2-3a489a8759ff">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <SharedWithUsers xmlns="c7fc7845-db9b-43ce-aae6-d5b1cef6895c">
+      <UserInfo>
+        <DisplayName>Christophe PLATEL</DisplayName>
+        <AccountId>72</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Média Paléo</DisplayName>
+        <AccountId>793</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Presse@paleo.ch</DisplayName>
+        <AccountId>800</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Malika DJEHICHE</DisplayName>
+        <AccountId>276</AccountId>
+        <AccountType/>
+      </UserInfo>
+      <UserInfo>
+        <DisplayName>Michèle MÜLLER</DisplayName>
+        <AccountId>56</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{824AA0DB-AE4F-4333-AC16-D49240DD4D4A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48ACF598-18E0-4DC7-83FB-D34FC7BFC7EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="849af248-afc5-4274-81e2-3a489a8759ff"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="c7fc7845-db9b-43ce-aae6-d5b1cef6895c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5365,9 +6099,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48ACF598-18E0-4DC7-83FB-D34FC7BFC7EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{824AA0DB-AE4F-4333-AC16-D49240DD4D4A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="849af248-afc5-4274-81e2-3a489a8759ff"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c7fc7845-db9b-43ce-aae6-d5b1cef6895c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>